--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22202"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Datum</t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Gesprek met de tutor</t>
+  </si>
+  <si>
+    <t>Voorbereiden voor gesprek met opdrachtgever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Het rapport maken voor de presentatie </t>
+  </si>
+  <si>
+    <t>Puntjes op de ï zetten voor het gesprek met de opdrachtgever</t>
+  </si>
+  <si>
+    <t>Gesprek met de opdrachtgever</t>
+  </si>
+  <si>
+    <t>Presentatie over ons rapport</t>
+  </si>
+  <si>
+    <t>Punten van de vergadering met de opdrachtgever op een rijtje gezet</t>
+  </si>
+  <si>
+    <t>Begin gemaakt met de Main app</t>
   </si>
 </sst>
 </file>
@@ -534,34 +555,62 @@
       <c r="A11" s="3">
         <v>41023</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="3">
+        <v>41024</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+      <c r="A13" s="3">
+        <v>41024</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="3">
+        <v>41025</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3">
+        <v>41025</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="3">
+        <v>41026</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="3">
+        <v>41026</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="4"/>
+      <c r="A18" s="3">
+        <v>41035</v>
+      </c>
       <c r="B18" s="4"/>
     </row>
     <row r="19" spans="1:2">

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Datum</t>
   </si>
@@ -70,6 +70,15 @@
   </si>
   <si>
     <t>Begin gemaakt met de Main app</t>
+  </si>
+  <si>
+    <t>Aan de Main app gewerkt</t>
+  </si>
+  <si>
+    <t>De Main App verder uitgewerkt: de settings + de map</t>
+  </si>
+  <si>
+    <t>Verder gewerkt aan de Main App: Lijst toegevoegd + data aangemaakt + settingspagina geoptimaliseerd</t>
   </si>
 </sst>
 </file>
@@ -467,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="1" customWidth="1"/>
@@ -609,28 +618,48 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3">
-        <v>41035</v>
-      </c>
-      <c r="B18" s="4"/>
+        <v>41036</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+      <c r="A19" s="3">
+        <v>41036</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="3">
+        <v>41037</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="3">
+        <v>41037</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="3">
+        <v>41038</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="4"/>
+      <c r="A23" s="3">
+        <v>41039</v>
+      </c>
       <c r="B23" s="4"/>
     </row>
     <row r="24" spans="1:2">
@@ -759,6 +788,10 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Datum</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Verder gewerkt aan de Main App: Lijst toegevoegd + data aangemaakt + settingspagina geoptimaliseerd</t>
+  </si>
+  <si>
+    <t>Aan de Main app gewerkt: Map, lijst en settings geoptimaliseerd + data verwerken nu vanaf gml</t>
   </si>
 </sst>
 </file>
@@ -660,11 +663,17 @@
       <c r="A23" s="3">
         <v>41039</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="3">
+        <v>41040</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4"/>

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="9660" yWindow="880" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Datum</t>
   </si>
@@ -82,6 +82,15 @@
   </si>
   <si>
     <t>Aan de Main app gewerkt: Map, lijst en settings geoptimaliseerd + data verwerken nu vanaf gml</t>
+  </si>
+  <si>
+    <t>De Main App verder uitgewerkt: Bugs fixen en optimaliseren</t>
+  </si>
+  <si>
+    <t>De Main App verder uitgewerkt: trail gemaakt op kaart + annotations verbeterd</t>
+  </si>
+  <si>
+    <t>De Main App verder gewerkt: Detailpagina + settings</t>
   </si>
 </sst>
 </file>
@@ -676,27 +685,49 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="3">
+        <v>41043</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="3">
+        <v>41043</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="A27" s="3">
+        <v>41044</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+      <c r="A28" s="3">
+        <v>41044</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="A29" s="3">
+        <v>41045</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="4"/>
+      <c r="A30" s="3">
+        <v>41050</v>
+      </c>
       <c r="B30" s="4"/>
     </row>
     <row r="31" spans="1:2">

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="880" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -91,6 +91,21 @@
   </si>
   <si>
     <t>De Main App verder gewerkt: Detailpagina + settings</t>
+  </si>
+  <si>
+    <t>De Main App bijgewerkt: betere code</t>
+  </si>
+  <si>
+    <t>Begin gemaakt met het Rapport</t>
+  </si>
+  <si>
+    <t>De gegevensconverter bijgewerkt</t>
+  </si>
+  <si>
+    <t>De Main App bijgewerkt: bugs fixen + code opruimen</t>
+  </si>
+  <si>
+    <t>Verder gewerkt aan het Rapport</t>
   </si>
 </sst>
 </file>
@@ -488,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="1" customWidth="1"/>
@@ -728,31 +743,57 @@
       <c r="A30" s="3">
         <v>41050</v>
       </c>
-      <c r="B30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="3">
+        <v>41050</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="3">
+        <v>41050</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="A33" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+      <c r="A34" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
+      <c r="A36" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="4"/>
@@ -832,6 +873,10 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>Datum</t>
   </si>
@@ -106,6 +106,21 @@
   </si>
   <si>
     <t>Verder gewerkt aan het Rapport</t>
+  </si>
+  <si>
+    <t>De annotations op de kaart verbeterd</t>
+  </si>
+  <si>
+    <t>Detailpagina geoptimaliseerd</t>
+  </si>
+  <si>
+    <t>Bugs fixen</t>
+  </si>
+  <si>
+    <t>Deelrapport gemaakt</t>
+  </si>
+  <si>
+    <t>Searchbar op de map verwijderd + settings voor iPhone verbeterd</t>
   </si>
 </sst>
 </file>
@@ -796,32 +811,58 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="3">
+        <v>41052</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="A38" s="3">
+        <v>41052</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="3">
+        <v>41052</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="3">
+        <v>41053</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4"/>
+      <c r="A41" s="3">
+        <v>41054</v>
+      </c>
       <c r="B41" s="4"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="A42" s="3">
+        <v>41058</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="3">
+        <v>41058</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4"/>

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="2480" yWindow="5440" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -121,6 +121,21 @@
   </si>
   <si>
     <t>Searchbar op de map verwijderd + settings voor iPhone verbeterd</t>
+  </si>
+  <si>
+    <t>Annations op de kaart bijgewerkt</t>
+  </si>
+  <si>
+    <t>Data er in verwerken</t>
+  </si>
+  <si>
+    <t>Het Rapport optimaliseren</t>
+  </si>
+  <si>
+    <t>Apps afgemaakt: De 3 verschillende Apps gesplitst zodat er 3 Apps onstaan</t>
+  </si>
+  <si>
+    <t>De laatste bugs gefixed van de Main-App</t>
   </si>
 </sst>
 </file>
@@ -133,6 +148,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -846,7 +862,9 @@
       <c r="A41" s="3">
         <v>41054</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="3">
@@ -865,24 +883,44 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
+      <c r="A44" s="3">
+        <v>41059</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+      <c r="A45" s="3">
+        <v>41060</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
+      <c r="A46" s="3">
+        <v>41061</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="3">
+        <v>41064</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="3">
+        <v>41065</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="4"/>

--- a/Logboeken/Logboek projectgroep.xlsx
+++ b/Logboeken/Logboek projectgroep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="5440" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Datum</t>
   </si>
@@ -136,6 +136,15 @@
   </si>
   <si>
     <t>De laatste bugs gefixed van de Main-App</t>
+  </si>
+  <si>
+    <t>Bugs fixen van de verschillende apps</t>
+  </si>
+  <si>
+    <t>Apps klaargemaakt voor gesprek met opdrachtgever</t>
+  </si>
+  <si>
+    <t>Rapport volledig gemaakt</t>
   </si>
 </sst>
 </file>
@@ -923,16 +932,28 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
+      <c r="A49" s="3">
+        <v>41066</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
+      <c r="A50" s="3">
+        <v>41067</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
+      <c r="A51" s="3">
+        <v>41071</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4"/>
